--- a/attendance/attendance.xlsx
+++ b/attendance/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,7 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20:08:45</t>
+          <t>21:18:52</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Present</t>
         </is>
       </c>
     </row>

--- a/attendance/attendance.xlsx
+++ b/attendance/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,28 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RTU24101CS049</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>21:18:52</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Present</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
